--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,6 +942,2024 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121394282</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>559438</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121394263</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559444</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6624248</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121394298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559319</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6624359</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121394258</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94700</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>210</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559431</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6624255</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121394291</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90468</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559369</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6624275</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121394279</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559456</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6624254</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121394281</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>559438</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6624241</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121394260</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>559431</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6624255</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121394261</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>559444</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6624248</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121394283</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>559438</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6624241</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121394280</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>559448</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6624275</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121394299</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559316</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6624382</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121394254</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>559346</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6624311</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121394292</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>559369</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6624275</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121394301</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>559363</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6624449</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121394256</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90914</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>559346</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6624311</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121394278</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90914</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>559405</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6624224</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121394300</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>559350</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6624430</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121394293</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>559369</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6624275</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394282</v>
+        <v>121394300</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,38 +956,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R4" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394263</v>
+        <v>121394301</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>95628</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559444</v>
+        <v>559363</v>
       </c>
       <c r="R5" t="n">
-        <v>6624248</v>
+        <v>6624449</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,12 +1124,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1156,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394298</v>
+        <v>121394279</v>
       </c>
       <c r="B6" t="n">
-        <v>95628</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559319</v>
+        <v>559456</v>
       </c>
       <c r="R6" t="n">
-        <v>6624359</v>
+        <v>6624254</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1262,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394258</v>
+        <v>121394256</v>
       </c>
       <c r="B7" t="n">
-        <v>94700</v>
+        <v>90914</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559431</v>
+        <v>559346</v>
       </c>
       <c r="R7" t="n">
-        <v>6624255</v>
+        <v>6624311</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,7 +1361,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1368,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394291</v>
+        <v>121394258</v>
       </c>
       <c r="B8" t="n">
-        <v>90468</v>
+        <v>94700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559369</v>
+        <v>559431</v>
       </c>
       <c r="R8" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1442,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1467,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394279</v>
+        <v>121394280</v>
       </c>
       <c r="B9" t="n">
-        <v>90662</v>
+        <v>95628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559456</v>
+        <v>559448</v>
       </c>
       <c r="R9" t="n">
-        <v>6624254</v>
+        <v>6624275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394281</v>
+        <v>121394254</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>90662</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1600,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559438</v>
+        <v>559346</v>
       </c>
       <c r="R10" t="n">
-        <v>6624241</v>
+        <v>6624311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,12 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394260</v>
+        <v>121394293</v>
       </c>
       <c r="B11" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559431</v>
+        <v>559369</v>
       </c>
       <c r="R11" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,7 +1785,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1792,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394261</v>
+        <v>121394278</v>
       </c>
       <c r="B12" t="n">
-        <v>5169</v>
+        <v>90914</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,25 +1808,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559444</v>
+        <v>559405</v>
       </c>
       <c r="R12" t="n">
-        <v>6624248</v>
+        <v>6624224</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,12 +1866,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1891,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1898,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394283</v>
+        <v>121394292</v>
       </c>
       <c r="B13" t="n">
         <v>95628</v>
@@ -1938,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R13" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2004,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394280</v>
+        <v>121394260</v>
       </c>
       <c r="B14" t="n">
-        <v>95628</v>
+        <v>90662</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2020,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559448</v>
+        <v>559431</v>
       </c>
       <c r="R14" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2110,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394299</v>
+        <v>121394283</v>
       </c>
       <c r="B15" t="n">
-        <v>95375</v>
+        <v>95628</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,25 +2126,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559316</v>
+        <v>559438</v>
       </c>
       <c r="R15" t="n">
-        <v>6624382</v>
+        <v>6624241</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2216,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394254</v>
+        <v>121394298</v>
       </c>
       <c r="B16" t="n">
-        <v>90662</v>
+        <v>95628</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,25 +2232,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559346</v>
+        <v>559319</v>
       </c>
       <c r="R16" t="n">
-        <v>6624311</v>
+        <v>6624359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2286,12 +2290,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2322,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394292</v>
+        <v>121394263</v>
       </c>
       <c r="B17" t="n">
-        <v>95628</v>
+        <v>5189</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,25 +2338,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R17" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,12 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394301</v>
+        <v>121394282</v>
       </c>
       <c r="B18" t="n">
-        <v>95628</v>
+        <v>5189</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559363</v>
+        <v>559438</v>
       </c>
       <c r="R18" t="n">
-        <v>6624449</v>
+        <v>6624241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2534,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394256</v>
+        <v>121394299</v>
       </c>
       <c r="B19" t="n">
-        <v>90914</v>
+        <v>95375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1101</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559346</v>
+        <v>559316</v>
       </c>
       <c r="R19" t="n">
-        <v>6624311</v>
+        <v>6624382</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2604,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,7 +2633,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2640,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394278</v>
+        <v>121394281</v>
       </c>
       <c r="B20" t="n">
-        <v>90914</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1101</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2680,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559405</v>
+        <v>559438</v>
       </c>
       <c r="R20" t="n">
-        <v>6624224</v>
+        <v>6624241</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2746,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394300</v>
+        <v>121394261</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2758,42 +2762,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559350</v>
+        <v>559444</v>
       </c>
       <c r="R21" t="n">
-        <v>6624430</v>
+        <v>6624248</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394293</v>
+        <v>121394291</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>90468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394300</v>
+        <v>121394280</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>95641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,42 +956,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559350</v>
+        <v>559448</v>
       </c>
       <c r="R4" t="n">
-        <v>6624430</v>
+        <v>6624275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394301</v>
+        <v>121394293</v>
       </c>
       <c r="B5" t="n">
-        <v>95628</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559363</v>
+        <v>559369</v>
       </c>
       <c r="R5" t="n">
-        <v>6624449</v>
+        <v>6624275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394279</v>
+        <v>121394263</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1200,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559456</v>
+        <v>559444</v>
       </c>
       <c r="R6" t="n">
-        <v>6624254</v>
+        <v>6624248</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1251,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1266,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394256</v>
+        <v>121394258</v>
       </c>
       <c r="B7" t="n">
-        <v>90914</v>
+        <v>94712</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1101</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559346</v>
+        <v>559431</v>
       </c>
       <c r="R7" t="n">
-        <v>6624311</v>
+        <v>6624255</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,7 +1357,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1372,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394258</v>
+        <v>121394279</v>
       </c>
       <c r="B8" t="n">
-        <v>94700</v>
+        <v>90674</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559431</v>
+        <v>559456</v>
       </c>
       <c r="R8" t="n">
-        <v>6624255</v>
+        <v>6624254</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394280</v>
+        <v>121394260</v>
       </c>
       <c r="B9" t="n">
-        <v>95628</v>
+        <v>90674</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559448</v>
+        <v>559431</v>
       </c>
       <c r="R9" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1587,7 +1583,7 @@
         <v>121394254</v>
       </c>
       <c r="B10" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1690,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394293</v>
+        <v>121394299</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>95388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1698,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559369</v>
+        <v>559316</v>
       </c>
       <c r="R11" t="n">
-        <v>6624275</v>
+        <v>6624382</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394278</v>
+        <v>121394292</v>
       </c>
       <c r="B12" t="n">
-        <v>90914</v>
+        <v>95641</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559405</v>
+        <v>559369</v>
       </c>
       <c r="R12" t="n">
-        <v>6624224</v>
+        <v>6624275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394292</v>
+        <v>121394291</v>
       </c>
       <c r="B13" t="n">
-        <v>95628</v>
+        <v>90480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1910,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394260</v>
+        <v>121394300</v>
       </c>
       <c r="B14" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,38 +2016,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559431</v>
+        <v>559350</v>
       </c>
       <c r="R14" t="n">
-        <v>6624255</v>
+        <v>6624430</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394283</v>
+        <v>121394281</v>
       </c>
       <c r="B15" t="n">
-        <v>95628</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2126,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394298</v>
+        <v>121394301</v>
       </c>
       <c r="B16" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559319</v>
+        <v>559363</v>
       </c>
       <c r="R16" t="n">
-        <v>6624359</v>
+        <v>6624449</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394263</v>
+        <v>121394261</v>
       </c>
       <c r="B17" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394282</v>
+        <v>121394278</v>
       </c>
       <c r="B18" t="n">
-        <v>5189</v>
+        <v>90926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559438</v>
+        <v>559405</v>
       </c>
       <c r="R18" t="n">
-        <v>6624241</v>
+        <v>6624224</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394299</v>
+        <v>121394283</v>
       </c>
       <c r="B19" t="n">
-        <v>95375</v>
+        <v>95641</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559316</v>
+        <v>559438</v>
       </c>
       <c r="R19" t="n">
-        <v>6624382</v>
+        <v>6624241</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394281</v>
+        <v>121394256</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>90926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559438</v>
+        <v>559346</v>
       </c>
       <c r="R20" t="n">
-        <v>6624241</v>
+        <v>6624311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394261</v>
+        <v>121394282</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559444</v>
+        <v>559438</v>
       </c>
       <c r="R21" t="n">
-        <v>6624248</v>
+        <v>6624241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394291</v>
+        <v>121394298</v>
       </c>
       <c r="B22" t="n">
-        <v>90468</v>
+        <v>95641</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559369</v>
+        <v>559319</v>
       </c>
       <c r="R22" t="n">
-        <v>6624275</v>
+        <v>6624359</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394280</v>
+        <v>121394299</v>
       </c>
       <c r="B4" t="n">
-        <v>95641</v>
+        <v>95389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,25 +956,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559448</v>
+        <v>559316</v>
       </c>
       <c r="R4" t="n">
-        <v>6624275</v>
+        <v>6624382</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394293</v>
+        <v>121394283</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>95642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R5" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394263</v>
+        <v>121394261</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394258</v>
+        <v>121394293</v>
       </c>
       <c r="B7" t="n">
-        <v>94712</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559431</v>
+        <v>559369</v>
       </c>
       <c r="R7" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394279</v>
+        <v>121394258</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
+        <v>94713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559456</v>
+        <v>559431</v>
       </c>
       <c r="R8" t="n">
-        <v>6624254</v>
+        <v>6624255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394260</v>
+        <v>121394292</v>
       </c>
       <c r="B9" t="n">
-        <v>90674</v>
+        <v>95642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559431</v>
+        <v>559369</v>
       </c>
       <c r="R9" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394254</v>
+        <v>121394263</v>
       </c>
       <c r="B10" t="n">
-        <v>90674</v>
+        <v>5189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559346</v>
+        <v>559444</v>
       </c>
       <c r="R10" t="n">
-        <v>6624311</v>
+        <v>6624248</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394299</v>
+        <v>121394301</v>
       </c>
       <c r="B11" t="n">
-        <v>95388</v>
+        <v>95642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,25 +1698,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559316</v>
+        <v>559363</v>
       </c>
       <c r="R11" t="n">
-        <v>6624382</v>
+        <v>6624449</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394292</v>
+        <v>121394254</v>
       </c>
       <c r="B12" t="n">
-        <v>95641</v>
+        <v>90675</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559369</v>
+        <v>559346</v>
       </c>
       <c r="R12" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394291</v>
+        <v>121394278</v>
       </c>
       <c r="B13" t="n">
-        <v>90480</v>
+        <v>90927</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,25 +1910,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>1101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559369</v>
+        <v>559405</v>
       </c>
       <c r="R13" t="n">
-        <v>6624275</v>
+        <v>6624224</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394300</v>
+        <v>121394260</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,42 +2016,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559350</v>
+        <v>559431</v>
       </c>
       <c r="R14" t="n">
-        <v>6624430</v>
+        <v>6624255</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,12 +2074,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,7 +2099,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2114,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394281</v>
+        <v>121394291</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>90481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,21 +2126,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R15" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2220,10 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394301</v>
+        <v>121394298</v>
       </c>
       <c r="B16" t="n">
-        <v>95641</v>
+        <v>95642</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559363</v>
+        <v>559319</v>
       </c>
       <c r="R16" t="n">
-        <v>6624449</v>
+        <v>6624359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,10 +2322,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394261</v>
+        <v>121394256</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
+        <v>90927</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,25 +2334,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559444</v>
+        <v>559346</v>
       </c>
       <c r="R17" t="n">
-        <v>6624248</v>
+        <v>6624311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394278</v>
+        <v>121394281</v>
       </c>
       <c r="B18" t="n">
-        <v>90926</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1101</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559405</v>
+        <v>559438</v>
       </c>
       <c r="R18" t="n">
-        <v>6624224</v>
+        <v>6624241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394283</v>
+        <v>121394300</v>
       </c>
       <c r="B19" t="n">
-        <v>95641</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,38 +2546,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R19" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394256</v>
+        <v>121394279</v>
       </c>
       <c r="B20" t="n">
-        <v>90926</v>
+        <v>90675</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559346</v>
+        <v>559456</v>
       </c>
       <c r="R20" t="n">
-        <v>6624311</v>
+        <v>6624254</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394282</v>
+        <v>121394280</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>95642</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559438</v>
+        <v>559448</v>
       </c>
       <c r="R21" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394298</v>
+        <v>121394282</v>
       </c>
       <c r="B22" t="n">
-        <v>95641</v>
+        <v>5189</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559319</v>
+        <v>559438</v>
       </c>
       <c r="R22" t="n">
-        <v>6624359</v>
+        <v>6624241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394299</v>
+        <v>121394254</v>
       </c>
       <c r="B4" t="n">
-        <v>95389</v>
+        <v>90678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559316</v>
+        <v>559346</v>
       </c>
       <c r="R4" t="n">
-        <v>6624382</v>
+        <v>6624311</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394283</v>
+        <v>121394291</v>
       </c>
       <c r="B5" t="n">
-        <v>95642</v>
+        <v>90484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R5" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394261</v>
+        <v>121394279</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>90678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559444</v>
+        <v>559456</v>
       </c>
       <c r="R6" t="n">
-        <v>6624248</v>
+        <v>6624254</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1265,7 +1265,7 @@
         <v>121394293</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394258</v>
+        <v>121394278</v>
       </c>
       <c r="B8" t="n">
-        <v>94713</v>
+        <v>90930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,25 +1380,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559431</v>
+        <v>559405</v>
       </c>
       <c r="R8" t="n">
-        <v>6624255</v>
+        <v>6624224</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394292</v>
+        <v>121394261</v>
       </c>
       <c r="B9" t="n">
-        <v>95642</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R9" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394263</v>
+        <v>121394280</v>
       </c>
       <c r="B10" t="n">
-        <v>5189</v>
+        <v>95645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559444</v>
+        <v>559448</v>
       </c>
       <c r="R10" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394301</v>
+        <v>121394300</v>
       </c>
       <c r="B11" t="n">
-        <v>95642</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,38 +1698,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559363</v>
+        <v>559350</v>
       </c>
       <c r="R11" t="n">
-        <v>6624449</v>
+        <v>6624430</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394254</v>
+        <v>121394256</v>
       </c>
       <c r="B12" t="n">
-        <v>90675</v>
+        <v>90930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,25 +1808,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1101</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,7 +1891,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1898,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394278</v>
+        <v>121394299</v>
       </c>
       <c r="B13" t="n">
-        <v>90927</v>
+        <v>95392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1101</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559405</v>
+        <v>559316</v>
       </c>
       <c r="R13" t="n">
-        <v>6624224</v>
+        <v>6624382</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2004,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394260</v>
+        <v>121394258</v>
       </c>
       <c r="B14" t="n">
-        <v>90675</v>
+        <v>94716</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2110,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394291</v>
+        <v>121394281</v>
       </c>
       <c r="B15" t="n">
-        <v>90481</v>
+        <v>5172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3215</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R15" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2216,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394298</v>
+        <v>121394283</v>
       </c>
       <c r="B16" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559319</v>
+        <v>559438</v>
       </c>
       <c r="R16" t="n">
-        <v>6624359</v>
+        <v>6624241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2322,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394256</v>
+        <v>121394301</v>
       </c>
       <c r="B17" t="n">
-        <v>90927</v>
+        <v>95645</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559346</v>
+        <v>559363</v>
       </c>
       <c r="R17" t="n">
-        <v>6624311</v>
+        <v>6624449</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,12 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394281</v>
+        <v>121394260</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>90678</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,21 +2448,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559438</v>
+        <v>559431</v>
       </c>
       <c r="R18" t="n">
-        <v>6624241</v>
+        <v>6624255</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2498,12 +2502,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,7 +2527,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2534,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394300</v>
+        <v>121394282</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>5192</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,42 +2550,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559350</v>
+        <v>559438</v>
       </c>
       <c r="R19" t="n">
-        <v>6624430</v>
+        <v>6624241</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394279</v>
+        <v>121394263</v>
       </c>
       <c r="B20" t="n">
-        <v>90675</v>
+        <v>5192</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559456</v>
+        <v>559444</v>
       </c>
       <c r="R20" t="n">
-        <v>6624254</v>
+        <v>6624248</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394280</v>
+        <v>121394298</v>
       </c>
       <c r="B21" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559448</v>
+        <v>559319</v>
       </c>
       <c r="R21" t="n">
-        <v>6624275</v>
+        <v>6624359</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394282</v>
+        <v>121394292</v>
       </c>
       <c r="B22" t="n">
-        <v>5189</v>
+        <v>95645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R22" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394254</v>
+        <v>121394261</v>
       </c>
       <c r="B4" t="n">
-        <v>90678</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559346</v>
+        <v>559444</v>
       </c>
       <c r="R4" t="n">
-        <v>6624311</v>
+        <v>6624248</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394291</v>
+        <v>121394283</v>
       </c>
       <c r="B5" t="n">
-        <v>90484</v>
+        <v>95645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R5" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394279</v>
+        <v>121394282</v>
       </c>
       <c r="B6" t="n">
-        <v>90678</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559456</v>
+        <v>559438</v>
       </c>
       <c r="R6" t="n">
-        <v>6624254</v>
+        <v>6624241</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394278</v>
+        <v>121394281</v>
       </c>
       <c r="B8" t="n">
-        <v>90930</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,25 +1380,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559405</v>
+        <v>559438</v>
       </c>
       <c r="R8" t="n">
-        <v>6624224</v>
+        <v>6624241</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394261</v>
+        <v>121394291</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>90484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559444</v>
+        <v>559369</v>
       </c>
       <c r="R9" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394280</v>
+        <v>121394299</v>
       </c>
       <c r="B10" t="n">
-        <v>95645</v>
+        <v>95392</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559448</v>
+        <v>559316</v>
       </c>
       <c r="R10" t="n">
-        <v>6624275</v>
+        <v>6624382</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394300</v>
+        <v>121394260</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,42 +1698,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559350</v>
+        <v>559431</v>
       </c>
       <c r="R11" t="n">
-        <v>6624430</v>
+        <v>6624255</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,12 +1756,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1796,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394256</v>
+        <v>121394263</v>
       </c>
       <c r="B12" t="n">
-        <v>90930</v>
+        <v>5192</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,25 +1804,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559346</v>
+        <v>559444</v>
       </c>
       <c r="R12" t="n">
-        <v>6624311</v>
+        <v>6624248</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1891,7 +1887,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1902,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394299</v>
+        <v>121394256</v>
       </c>
       <c r="B13" t="n">
-        <v>95392</v>
+        <v>90930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1910,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>1101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559316</v>
+        <v>559346</v>
       </c>
       <c r="R13" t="n">
-        <v>6624382</v>
+        <v>6624311</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,12 +1968,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +1993,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2008,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394258</v>
+        <v>121394301</v>
       </c>
       <c r="B14" t="n">
-        <v>94716</v>
+        <v>95645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559431</v>
+        <v>559363</v>
       </c>
       <c r="R14" t="n">
-        <v>6624255</v>
+        <v>6624449</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,12 +2074,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,7 +2099,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2114,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394281</v>
+        <v>121394300</v>
       </c>
       <c r="B15" t="n">
-        <v>5172</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,38 +2122,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R15" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394283</v>
+        <v>121394298</v>
       </c>
       <c r="B16" t="n">
         <v>95645</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559438</v>
+        <v>559319</v>
       </c>
       <c r="R16" t="n">
-        <v>6624241</v>
+        <v>6624359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394301</v>
+        <v>121394258</v>
       </c>
       <c r="B17" t="n">
-        <v>95645</v>
+        <v>94716</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,25 +2338,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559363</v>
+        <v>559431</v>
       </c>
       <c r="R17" t="n">
-        <v>6624449</v>
+        <v>6624255</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394260</v>
+        <v>121394278</v>
       </c>
       <c r="B18" t="n">
-        <v>90678</v>
+        <v>90930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1101</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559431</v>
+        <v>559405</v>
       </c>
       <c r="R18" t="n">
-        <v>6624255</v>
+        <v>6624224</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394282</v>
+        <v>121394292</v>
       </c>
       <c r="B19" t="n">
-        <v>5192</v>
+        <v>95645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R19" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394263</v>
+        <v>121394254</v>
       </c>
       <c r="B20" t="n">
-        <v>5192</v>
+        <v>90678</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559444</v>
+        <v>559346</v>
       </c>
       <c r="R20" t="n">
-        <v>6624248</v>
+        <v>6624311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,7 +2750,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394298</v>
+        <v>121394280</v>
       </c>
       <c r="B21" t="n">
         <v>95645</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559319</v>
+        <v>559448</v>
       </c>
       <c r="R21" t="n">
-        <v>6624359</v>
+        <v>6624275</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394292</v>
+        <v>121394279</v>
       </c>
       <c r="B22" t="n">
-        <v>95645</v>
+        <v>90678</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559369</v>
+        <v>559456</v>
       </c>
       <c r="R22" t="n">
-        <v>6624275</v>
+        <v>6624254</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394254</v>
+        <v>121394280</v>
       </c>
       <c r="B20" t="n">
-        <v>90678</v>
+        <v>95645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559346</v>
+        <v>559448</v>
       </c>
       <c r="R20" t="n">
-        <v>6624311</v>
+        <v>6624275</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394280</v>
+        <v>121394254</v>
       </c>
       <c r="B21" t="n">
-        <v>95645</v>
+        <v>90678</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559448</v>
+        <v>559346</v>
       </c>
       <c r="R21" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394261</v>
+        <v>121394280</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>95651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,25 +956,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559444</v>
+        <v>559448</v>
       </c>
       <c r="R4" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394283</v>
+        <v>121394281</v>
       </c>
       <c r="B5" t="n">
-        <v>95645</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394282</v>
+        <v>121394298</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>95651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559438</v>
+        <v>559319</v>
       </c>
       <c r="R6" t="n">
-        <v>6624241</v>
+        <v>6624359</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394293</v>
+        <v>121394283</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>95651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R7" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394281</v>
+        <v>121394260</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>90684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559438</v>
+        <v>559431</v>
       </c>
       <c r="R8" t="n">
-        <v>6624241</v>
+        <v>6624255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1477,7 +1477,7 @@
         <v>121394291</v>
       </c>
       <c r="B9" t="n">
-        <v>90484</v>
+        <v>90490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394299</v>
+        <v>121394301</v>
       </c>
       <c r="B10" t="n">
-        <v>95392</v>
+        <v>95651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559316</v>
+        <v>559363</v>
       </c>
       <c r="R10" t="n">
-        <v>6624382</v>
+        <v>6624449</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394260</v>
+        <v>121394261</v>
       </c>
       <c r="B11" t="n">
-        <v>90678</v>
+        <v>5172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559431</v>
+        <v>559444</v>
       </c>
       <c r="R11" t="n">
-        <v>6624255</v>
+        <v>6624248</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394263</v>
+        <v>121394282</v>
       </c>
       <c r="B12" t="n">
         <v>5192</v>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559444</v>
+        <v>559438</v>
       </c>
       <c r="R12" t="n">
-        <v>6624248</v>
+        <v>6624241</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1901,7 +1901,7 @@
         <v>121394256</v>
       </c>
       <c r="B13" t="n">
-        <v>90930</v>
+        <v>90936</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394301</v>
+        <v>121394254</v>
       </c>
       <c r="B14" t="n">
-        <v>95645</v>
+        <v>90684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559363</v>
+        <v>559346</v>
       </c>
       <c r="R14" t="n">
-        <v>6624449</v>
+        <v>6624311</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394300</v>
+        <v>121394279</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>90684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,42 +2122,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559350</v>
+        <v>559456</v>
       </c>
       <c r="R15" t="n">
-        <v>6624430</v>
+        <v>6624254</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2220,10 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394298</v>
+        <v>121394278</v>
       </c>
       <c r="B16" t="n">
-        <v>95645</v>
+        <v>90936</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,21 +2232,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559319</v>
+        <v>559405</v>
       </c>
       <c r="R16" t="n">
-        <v>6624359</v>
+        <v>6624224</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,10 +2322,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394258</v>
+        <v>121394292</v>
       </c>
       <c r="B17" t="n">
-        <v>94716</v>
+        <v>95651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,25 +2334,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559431</v>
+        <v>559369</v>
       </c>
       <c r="R17" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,12 +2392,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,7 +2417,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2432,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394278</v>
+        <v>121394263</v>
       </c>
       <c r="B18" t="n">
-        <v>90930</v>
+        <v>5192</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559405</v>
+        <v>559444</v>
       </c>
       <c r="R18" t="n">
-        <v>6624224</v>
+        <v>6624248</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,12 +2498,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2523,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2538,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394292</v>
+        <v>121394300</v>
       </c>
       <c r="B19" t="n">
-        <v>95645</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,38 +2546,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559369</v>
+        <v>559350</v>
       </c>
       <c r="R19" t="n">
-        <v>6624275</v>
+        <v>6624430</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394280</v>
+        <v>121394293</v>
       </c>
       <c r="B20" t="n">
-        <v>95645</v>
+        <v>90719</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559448</v>
+        <v>559369</v>
       </c>
       <c r="R20" t="n">
         <v>6624275</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394254</v>
+        <v>121394258</v>
       </c>
       <c r="B21" t="n">
-        <v>90678</v>
+        <v>94722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559346</v>
+        <v>559431</v>
       </c>
       <c r="R21" t="n">
-        <v>6624311</v>
+        <v>6624255</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394279</v>
+        <v>121394299</v>
       </c>
       <c r="B22" t="n">
-        <v>90678</v>
+        <v>95398</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559456</v>
+        <v>559316</v>
       </c>
       <c r="R22" t="n">
-        <v>6624254</v>
+        <v>6624382</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394280</v>
+        <v>121394300</v>
       </c>
       <c r="B4" t="n">
-        <v>95651</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,38 +956,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559448</v>
+        <v>559350</v>
       </c>
       <c r="R4" t="n">
-        <v>6624275</v>
+        <v>6624430</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394281</v>
+        <v>121394283</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>95652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1156,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394298</v>
+        <v>121394256</v>
       </c>
       <c r="B6" t="n">
-        <v>95651</v>
+        <v>90937</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1176,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559319</v>
+        <v>559346</v>
       </c>
       <c r="R6" t="n">
-        <v>6624359</v>
+        <v>6624311</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1230,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1255,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1262,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394283</v>
+        <v>121394298</v>
       </c>
       <c r="B7" t="n">
-        <v>95651</v>
+        <v>95652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559438</v>
+        <v>559319</v>
       </c>
       <c r="R7" t="n">
-        <v>6624241</v>
+        <v>6624359</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394260</v>
+        <v>121394301</v>
       </c>
       <c r="B8" t="n">
-        <v>90684</v>
+        <v>95652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559431</v>
+        <v>559363</v>
       </c>
       <c r="R8" t="n">
-        <v>6624255</v>
+        <v>6624449</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,12 +1442,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1467,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1474,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394291</v>
+        <v>121394263</v>
       </c>
       <c r="B9" t="n">
-        <v>90490</v>
+        <v>5192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R9" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394301</v>
+        <v>121394260</v>
       </c>
       <c r="B10" t="n">
-        <v>95651</v>
+        <v>90685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1596,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559363</v>
+        <v>559431</v>
       </c>
       <c r="R10" t="n">
-        <v>6624449</v>
+        <v>6624255</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,12 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394261</v>
+        <v>121394299</v>
       </c>
       <c r="B11" t="n">
-        <v>5172</v>
+        <v>95399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559444</v>
+        <v>559316</v>
       </c>
       <c r="R11" t="n">
-        <v>6624248</v>
+        <v>6624382</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,7 +1785,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1792,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394282</v>
+        <v>121394279</v>
       </c>
       <c r="B12" t="n">
-        <v>5192</v>
+        <v>90685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559438</v>
+        <v>559456</v>
       </c>
       <c r="R12" t="n">
-        <v>6624241</v>
+        <v>6624254</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1898,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394256</v>
+        <v>121394292</v>
       </c>
       <c r="B13" t="n">
-        <v>90936</v>
+        <v>95652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559346</v>
+        <v>559369</v>
       </c>
       <c r="R13" t="n">
-        <v>6624311</v>
+        <v>6624275</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,12 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2004,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394254</v>
+        <v>121394282</v>
       </c>
       <c r="B14" t="n">
-        <v>90684</v>
+        <v>5192</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559346</v>
+        <v>559438</v>
       </c>
       <c r="R14" t="n">
-        <v>6624311</v>
+        <v>6624241</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2110,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394279</v>
+        <v>121394258</v>
       </c>
       <c r="B15" t="n">
-        <v>90684</v>
+        <v>94723</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2150,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559456</v>
+        <v>559431</v>
       </c>
       <c r="R15" t="n">
-        <v>6624254</v>
+        <v>6624255</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2180,12 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2209,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2216,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394278</v>
+        <v>121394293</v>
       </c>
       <c r="B16" t="n">
-        <v>90936</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559405</v>
+        <v>559369</v>
       </c>
       <c r="R16" t="n">
-        <v>6624224</v>
+        <v>6624275</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2322,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394292</v>
+        <v>121394281</v>
       </c>
       <c r="B17" t="n">
-        <v>95651</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,25 +2338,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R17" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2428,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394263</v>
+        <v>121394280</v>
       </c>
       <c r="B18" t="n">
-        <v>5192</v>
+        <v>95652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559444</v>
+        <v>559448</v>
       </c>
       <c r="R18" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2498,12 +2502,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,7 +2527,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2534,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394300</v>
+        <v>121394291</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>90491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,42 +2550,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559350</v>
+        <v>559369</v>
       </c>
       <c r="R19" t="n">
-        <v>6624430</v>
+        <v>6624275</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394293</v>
+        <v>121394254</v>
       </c>
       <c r="B20" t="n">
-        <v>90719</v>
+        <v>90685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559369</v>
+        <v>559346</v>
       </c>
       <c r="R20" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394258</v>
+        <v>121394261</v>
       </c>
       <c r="B21" t="n">
-        <v>94722</v>
+        <v>5172</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559431</v>
+        <v>559444</v>
       </c>
       <c r="R21" t="n">
-        <v>6624255</v>
+        <v>6624248</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394299</v>
+        <v>121394278</v>
       </c>
       <c r="B22" t="n">
-        <v>95398</v>
+        <v>90937</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>1101</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559316</v>
+        <v>559405</v>
       </c>
       <c r="R22" t="n">
-        <v>6624382</v>
+        <v>6624224</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394300</v>
+        <v>121394292</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>95652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,42 +956,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559350</v>
+        <v>559369</v>
       </c>
       <c r="R4" t="n">
-        <v>6624430</v>
+        <v>6624275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1054,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394283</v>
+        <v>121394293</v>
       </c>
       <c r="B5" t="n">
-        <v>95652</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R5" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394256</v>
+        <v>121394254</v>
       </c>
       <c r="B6" t="n">
-        <v>90937</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1266,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394298</v>
+        <v>121394299</v>
       </c>
       <c r="B7" t="n">
-        <v>95652</v>
+        <v>95399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559319</v>
+        <v>559316</v>
       </c>
       <c r="R7" t="n">
-        <v>6624359</v>
+        <v>6624382</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394301</v>
+        <v>121394278</v>
       </c>
       <c r="B8" t="n">
-        <v>95652</v>
+        <v>90937</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559363</v>
+        <v>559405</v>
       </c>
       <c r="R8" t="n">
-        <v>6624449</v>
+        <v>6624224</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394263</v>
+        <v>121394291</v>
       </c>
       <c r="B9" t="n">
-        <v>5192</v>
+        <v>90491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559444</v>
+        <v>559369</v>
       </c>
       <c r="R9" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1584,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394260</v>
+        <v>121394256</v>
       </c>
       <c r="B10" t="n">
-        <v>90685</v>
+        <v>90937</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559431</v>
+        <v>559346</v>
       </c>
       <c r="R10" t="n">
-        <v>6624255</v>
+        <v>6624311</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394299</v>
+        <v>121394301</v>
       </c>
       <c r="B11" t="n">
-        <v>95399</v>
+        <v>95652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1698,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559316</v>
+        <v>559363</v>
       </c>
       <c r="R11" t="n">
-        <v>6624382</v>
+        <v>6624449</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394279</v>
+        <v>121394280</v>
       </c>
       <c r="B12" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,25 +1804,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559456</v>
+        <v>559448</v>
       </c>
       <c r="R12" t="n">
-        <v>6624254</v>
+        <v>6624275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394292</v>
+        <v>121394261</v>
       </c>
       <c r="B13" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1910,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R13" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,12 +1968,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +1993,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2008,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394282</v>
+        <v>121394300</v>
       </c>
       <c r="B14" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,38 +2016,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R14" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394258</v>
+        <v>121394279</v>
       </c>
       <c r="B15" t="n">
-        <v>94723</v>
+        <v>90685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559431</v>
+        <v>559456</v>
       </c>
       <c r="R15" t="n">
-        <v>6624255</v>
+        <v>6624254</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394293</v>
+        <v>121394282</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>5192</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R16" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394280</v>
+        <v>121394283</v>
       </c>
       <c r="B18" t="n">
         <v>95652</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559448</v>
+        <v>559438</v>
       </c>
       <c r="R18" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394291</v>
+        <v>121394258</v>
       </c>
       <c r="B19" t="n">
-        <v>90491</v>
+        <v>94723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,21 +2554,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559369</v>
+        <v>559431</v>
       </c>
       <c r="R19" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394254</v>
+        <v>121394298</v>
       </c>
       <c r="B20" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559346</v>
+        <v>559319</v>
       </c>
       <c r="R20" t="n">
-        <v>6624311</v>
+        <v>6624359</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394261</v>
+        <v>121394263</v>
       </c>
       <c r="B21" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,21 +2766,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394278</v>
+        <v>121394260</v>
       </c>
       <c r="B22" t="n">
-        <v>90937</v>
+        <v>90685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559405</v>
+        <v>559431</v>
       </c>
       <c r="R22" t="n">
-        <v>6624224</v>
+        <v>6624255</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394292</v>
+        <v>121394278</v>
       </c>
       <c r="B4" t="n">
-        <v>95652</v>
+        <v>90937</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559369</v>
+        <v>559405</v>
       </c>
       <c r="R4" t="n">
-        <v>6624275</v>
+        <v>6624224</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394293</v>
+        <v>121394299</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>95399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559369</v>
+        <v>559316</v>
       </c>
       <c r="R5" t="n">
-        <v>6624275</v>
+        <v>6624382</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394254</v>
+        <v>121394281</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>5172</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559346</v>
+        <v>559438</v>
       </c>
       <c r="R6" t="n">
-        <v>6624311</v>
+        <v>6624241</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394299</v>
+        <v>121394291</v>
       </c>
       <c r="B7" t="n">
-        <v>95399</v>
+        <v>90491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559316</v>
+        <v>559369</v>
       </c>
       <c r="R7" t="n">
-        <v>6624382</v>
+        <v>6624275</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394278</v>
+        <v>121394301</v>
       </c>
       <c r="B8" t="n">
-        <v>90937</v>
+        <v>95652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559405</v>
+        <v>559363</v>
       </c>
       <c r="R8" t="n">
-        <v>6624224</v>
+        <v>6624449</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394291</v>
+        <v>121394263</v>
       </c>
       <c r="B9" t="n">
-        <v>90491</v>
+        <v>5192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R9" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394256</v>
+        <v>121394300</v>
       </c>
       <c r="B10" t="n">
-        <v>90937</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,38 +1592,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559346</v>
+        <v>559350</v>
       </c>
       <c r="R10" t="n">
-        <v>6624311</v>
+        <v>6624430</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,12 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394301</v>
+        <v>121394280</v>
       </c>
       <c r="B11" t="n">
         <v>95652</v>
@@ -1726,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559363</v>
+        <v>559448</v>
       </c>
       <c r="R11" t="n">
-        <v>6624449</v>
+        <v>6624275</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394280</v>
+        <v>121394258</v>
       </c>
       <c r="B12" t="n">
-        <v>95652</v>
+        <v>94723</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,25 +1808,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559448</v>
+        <v>559431</v>
       </c>
       <c r="R12" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,12 +1866,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1891,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1898,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394261</v>
+        <v>121394292</v>
       </c>
       <c r="B13" t="n">
-        <v>5172</v>
+        <v>95652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559444</v>
+        <v>559369</v>
       </c>
       <c r="R13" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,12 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2004,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394300</v>
+        <v>121394293</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,42 +2020,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559350</v>
+        <v>559369</v>
       </c>
       <c r="R14" t="n">
-        <v>6624430</v>
+        <v>6624275</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394279</v>
+        <v>121394298</v>
       </c>
       <c r="B15" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2126,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559456</v>
+        <v>559319</v>
       </c>
       <c r="R15" t="n">
-        <v>6624254</v>
+        <v>6624359</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394281</v>
+        <v>121394254</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559438</v>
+        <v>559346</v>
       </c>
       <c r="R17" t="n">
-        <v>6624241</v>
+        <v>6624311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394283</v>
+        <v>121394261</v>
       </c>
       <c r="B18" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559438</v>
+        <v>559444</v>
       </c>
       <c r="R18" t="n">
-        <v>6624241</v>
+        <v>6624248</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394258</v>
+        <v>121394283</v>
       </c>
       <c r="B19" t="n">
-        <v>94723</v>
+        <v>95652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559431</v>
+        <v>559438</v>
       </c>
       <c r="R19" t="n">
-        <v>6624255</v>
+        <v>6624241</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394298</v>
+        <v>121394279</v>
       </c>
       <c r="B20" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559319</v>
+        <v>559456</v>
       </c>
       <c r="R20" t="n">
-        <v>6624359</v>
+        <v>6624254</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394263</v>
+        <v>121394256</v>
       </c>
       <c r="B21" t="n">
-        <v>5192</v>
+        <v>90937</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559444</v>
+        <v>559346</v>
       </c>
       <c r="R21" t="n">
-        <v>6624248</v>
+        <v>6624311</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394278</v>
+        <v>121394283</v>
       </c>
       <c r="B4" t="n">
-        <v>90937</v>
+        <v>95652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,21 +960,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559405</v>
+        <v>559438</v>
       </c>
       <c r="R4" t="n">
-        <v>6624224</v>
+        <v>6624241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394299</v>
+        <v>121394292</v>
       </c>
       <c r="B5" t="n">
-        <v>95399</v>
+        <v>95652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559316</v>
+        <v>559369</v>
       </c>
       <c r="R5" t="n">
-        <v>6624382</v>
+        <v>6624275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394281</v>
+        <v>121394300</v>
       </c>
       <c r="B6" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,38 +1168,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R6" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1262,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394291</v>
+        <v>121394281</v>
       </c>
       <c r="B7" t="n">
-        <v>90491</v>
+        <v>5172</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R7" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394301</v>
+        <v>121394298</v>
       </c>
       <c r="B8" t="n">
         <v>95652</v>
@@ -1408,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559363</v>
+        <v>559319</v>
       </c>
       <c r="R8" t="n">
-        <v>6624449</v>
+        <v>6624359</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394263</v>
+        <v>121394282</v>
       </c>
       <c r="B9" t="n">
         <v>5192</v>
@@ -1514,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559444</v>
+        <v>559438</v>
       </c>
       <c r="R9" t="n">
-        <v>6624248</v>
+        <v>6624241</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394300</v>
+        <v>121394299</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>95399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,42 +1596,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559350</v>
+        <v>559316</v>
       </c>
       <c r="R10" t="n">
-        <v>6624430</v>
+        <v>6624382</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394280</v>
+        <v>121394254</v>
       </c>
       <c r="B11" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559448</v>
+        <v>559346</v>
       </c>
       <c r="R11" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394258</v>
+        <v>121394291</v>
       </c>
       <c r="B12" t="n">
-        <v>94723</v>
+        <v>90491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559431</v>
+        <v>559369</v>
       </c>
       <c r="R12" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394292</v>
+        <v>121394280</v>
       </c>
       <c r="B13" t="n">
         <v>95652</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559369</v>
+        <v>559448</v>
       </c>
       <c r="R13" t="n">
         <v>6624275</v>
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394293</v>
+        <v>121394258</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>94723</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,25 +2020,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559369</v>
+        <v>559431</v>
       </c>
       <c r="R14" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394298</v>
+        <v>121394261</v>
       </c>
       <c r="B15" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2126,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559319</v>
+        <v>559444</v>
       </c>
       <c r="R15" t="n">
-        <v>6624359</v>
+        <v>6624248</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,12 +2184,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394282</v>
+        <v>121394293</v>
       </c>
       <c r="B16" t="n">
-        <v>5192</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R16" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394254</v>
+        <v>121394279</v>
       </c>
       <c r="B17" t="n">
         <v>90685</v>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559346</v>
+        <v>559456</v>
       </c>
       <c r="R17" t="n">
-        <v>6624311</v>
+        <v>6624254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394261</v>
+        <v>121394256</v>
       </c>
       <c r="B18" t="n">
-        <v>5172</v>
+        <v>90937</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559444</v>
+        <v>559346</v>
       </c>
       <c r="R18" t="n">
-        <v>6624248</v>
+        <v>6624311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394283</v>
+        <v>121394263</v>
       </c>
       <c r="B19" t="n">
-        <v>95652</v>
+        <v>5192</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559438</v>
+        <v>559444</v>
       </c>
       <c r="R19" t="n">
-        <v>6624241</v>
+        <v>6624248</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394279</v>
+        <v>121394260</v>
       </c>
       <c r="B20" t="n">
         <v>90685</v>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559456</v>
+        <v>559431</v>
       </c>
       <c r="R20" t="n">
-        <v>6624254</v>
+        <v>6624255</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2750,7 +2750,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394256</v>
+        <v>121394278</v>
       </c>
       <c r="B21" t="n">
         <v>90937</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559346</v>
+        <v>559405</v>
       </c>
       <c r="R21" t="n">
-        <v>6624311</v>
+        <v>6624224</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394260</v>
+        <v>121394301</v>
       </c>
       <c r="B22" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559431</v>
+        <v>559363</v>
       </c>
       <c r="R22" t="n">
-        <v>6624255</v>
+        <v>6624449</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -944,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394283</v>
+        <v>121394300</v>
       </c>
       <c r="B4" t="n">
-        <v>95652</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,38 +956,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559438</v>
+        <v>559350</v>
       </c>
       <c r="R4" t="n">
-        <v>6624241</v>
+        <v>6624430</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394292</v>
+        <v>121394291</v>
       </c>
       <c r="B5" t="n">
-        <v>95652</v>
+        <v>90498</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1156,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394300</v>
+        <v>121394293</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,42 +1172,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559350</v>
+        <v>559369</v>
       </c>
       <c r="R6" t="n">
-        <v>6624430</v>
+        <v>6624275</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394281</v>
+        <v>121394279</v>
       </c>
       <c r="B7" t="n">
-        <v>5172</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559438</v>
+        <v>559456</v>
       </c>
       <c r="R7" t="n">
-        <v>6624241</v>
+        <v>6624254</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394298</v>
+        <v>121394292</v>
       </c>
       <c r="B8" t="n">
-        <v>95652</v>
+        <v>95660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559319</v>
+        <v>559369</v>
       </c>
       <c r="R8" t="n">
-        <v>6624359</v>
+        <v>6624275</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394282</v>
+        <v>121394278</v>
       </c>
       <c r="B9" t="n">
-        <v>5192</v>
+        <v>90945</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559438</v>
+        <v>559405</v>
       </c>
       <c r="R9" t="n">
-        <v>6624241</v>
+        <v>6624224</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394299</v>
+        <v>121394283</v>
       </c>
       <c r="B10" t="n">
-        <v>95399</v>
+        <v>95660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1596,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559316</v>
+        <v>559438</v>
       </c>
       <c r="R10" t="n">
-        <v>6624382</v>
+        <v>6624241</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394254</v>
+        <v>121394299</v>
       </c>
       <c r="B11" t="n">
-        <v>90685</v>
+        <v>95407</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559346</v>
+        <v>559316</v>
       </c>
       <c r="R11" t="n">
-        <v>6624311</v>
+        <v>6624382</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394291</v>
+        <v>121394282</v>
       </c>
       <c r="B12" t="n">
-        <v>90491</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559369</v>
+        <v>559438</v>
       </c>
       <c r="R12" t="n">
-        <v>6624275</v>
+        <v>6624241</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394280</v>
+        <v>121394258</v>
       </c>
       <c r="B13" t="n">
-        <v>95652</v>
+        <v>94731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,25 +1914,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559448</v>
+        <v>559431</v>
       </c>
       <c r="R13" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394258</v>
+        <v>121394261</v>
       </c>
       <c r="B14" t="n">
-        <v>94723</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559431</v>
+        <v>559444</v>
       </c>
       <c r="R14" t="n">
-        <v>6624255</v>
+        <v>6624248</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394261</v>
+        <v>121394256</v>
       </c>
       <c r="B15" t="n">
-        <v>5172</v>
+        <v>90945</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2126,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>1101</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559444</v>
+        <v>559346</v>
       </c>
       <c r="R15" t="n">
-        <v>6624248</v>
+        <v>6624311</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394293</v>
+        <v>121394280</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>95660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559369</v>
+        <v>559448</v>
       </c>
       <c r="R16" t="n">
         <v>6624275</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394279</v>
+        <v>121394301</v>
       </c>
       <c r="B17" t="n">
-        <v>90685</v>
+        <v>95660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,25 +2338,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559456</v>
+        <v>559363</v>
       </c>
       <c r="R17" t="n">
-        <v>6624254</v>
+        <v>6624449</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394256</v>
+        <v>121394260</v>
       </c>
       <c r="B18" t="n">
-        <v>90937</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2444,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559346</v>
+        <v>559431</v>
       </c>
       <c r="R18" t="n">
-        <v>6624311</v>
+        <v>6624255</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394263</v>
+        <v>121394298</v>
       </c>
       <c r="B19" t="n">
-        <v>5192</v>
+        <v>95660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559444</v>
+        <v>559319</v>
       </c>
       <c r="R19" t="n">
-        <v>6624248</v>
+        <v>6624359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Lotta Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394260</v>
+        <v>121394254</v>
       </c>
       <c r="B20" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559431</v>
+        <v>559346</v>
       </c>
       <c r="R20" t="n">
-        <v>6624255</v>
+        <v>6624311</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394278</v>
+        <v>121394263</v>
       </c>
       <c r="B21" t="n">
-        <v>90937</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2762,25 +2762,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559405</v>
+        <v>559444</v>
       </c>
       <c r="R21" t="n">
-        <v>6624224</v>
+        <v>6624248</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2856,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121394301</v>
+        <v>121394281</v>
       </c>
       <c r="B22" t="n">
-        <v>95652</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>559363</v>
+        <v>559438</v>
       </c>
       <c r="R22" t="n">
-        <v>6624449</v>
+        <v>6624241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -1054,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394291</v>
+        <v>121394293</v>
       </c>
       <c r="B5" t="n">
-        <v>90498</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,25 +1066,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394293</v>
+        <v>121394291</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>90498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113361934</v>
+        <v>121394258</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>94731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,57 +818,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vålbo NNV om (knärot), Vstm</t>
+          <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559374</v>
+        <v>559431</v>
       </c>
       <c r="R3" t="n">
         <v>6624255</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,24 +874,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>U-Sur-0550</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>minst. 1 blommande + tiotal rosetter foto i AP OK</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,38 +890,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lennart Eriksson R, Mikael Mälberg</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394258</v>
+        <v>121394280</v>
       </c>
       <c r="B4" t="n">
-        <v>94731</v>
+        <v>95660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,25 +924,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559431</v>
+        <v>559448</v>
       </c>
       <c r="R4" t="n">
-        <v>6624255</v>
+        <v>6624275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394280</v>
+        <v>121394254</v>
       </c>
       <c r="B5" t="n">
-        <v>95660</v>
+        <v>90693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559448</v>
+        <v>559346</v>
       </c>
       <c r="R5" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1113,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1156,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394254</v>
+        <v>121394291</v>
       </c>
       <c r="B6" t="n">
-        <v>90693</v>
+        <v>90498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559346</v>
+        <v>559369</v>
       </c>
       <c r="R6" t="n">
-        <v>6624311</v>
+        <v>6624275</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,12 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1219,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1262,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394291</v>
+        <v>121394260</v>
       </c>
       <c r="B7" t="n">
-        <v>90498</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559369</v>
+        <v>559431</v>
       </c>
       <c r="R7" t="n">
-        <v>6624275</v>
+        <v>6624255</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,12 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1325,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1368,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394260</v>
+        <v>121394261</v>
       </c>
       <c r="B8" t="n">
-        <v>90693</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559431</v>
+        <v>559444</v>
       </c>
       <c r="R8" t="n">
-        <v>6624255</v>
+        <v>6624248</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394261</v>
+        <v>121394293</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559444</v>
+        <v>559369</v>
       </c>
       <c r="R9" t="n">
-        <v>6624248</v>
+        <v>6624275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,12 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1580,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394293</v>
+        <v>121394263</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559369</v>
+        <v>559444</v>
       </c>
       <c r="R10" t="n">
-        <v>6624275</v>
+        <v>6624248</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,12 +1618,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1643,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1686,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121394263</v>
+        <v>121394278</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>90945</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,25 +1666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559444</v>
+        <v>559405</v>
       </c>
       <c r="R11" t="n">
-        <v>6624248</v>
+        <v>6624224</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,12 +1724,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,7 +1749,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1792,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394278</v>
+        <v>121394301</v>
       </c>
       <c r="B12" t="n">
-        <v>90945</v>
+        <v>95660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559405</v>
+        <v>559363</v>
       </c>
       <c r="R12" t="n">
-        <v>6624224</v>
+        <v>6624449</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1898,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394301</v>
+        <v>121394300</v>
       </c>
       <c r="B13" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,38 +1878,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559363</v>
+        <v>559350</v>
       </c>
       <c r="R13" t="n">
-        <v>6624449</v>
+        <v>6624430</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2004,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394300</v>
+        <v>121394283</v>
       </c>
       <c r="B14" t="n">
-        <v>98113</v>
+        <v>95660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,42 +1988,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559350</v>
+        <v>559438</v>
       </c>
       <c r="R14" t="n">
-        <v>6624430</v>
+        <v>6624241</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394283</v>
+        <v>121394256</v>
       </c>
       <c r="B15" t="n">
-        <v>95660</v>
+        <v>90945</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,21 +2098,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>559438</v>
+        <v>559346</v>
       </c>
       <c r="R15" t="n">
-        <v>6624241</v>
+        <v>6624311</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,12 +2152,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2177,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Lotta Lundmark, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2220,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394256</v>
+        <v>121394298</v>
       </c>
       <c r="B16" t="n">
-        <v>90945</v>
+        <v>95660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559346</v>
+        <v>559319</v>
       </c>
       <c r="R16" t="n">
-        <v>6624311</v>
+        <v>6624359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,12 +2258,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,7 +2283,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2326,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394298</v>
+        <v>121394292</v>
       </c>
       <c r="B17" t="n">
         <v>95660</v>
@@ -2366,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559319</v>
+        <v>559369</v>
       </c>
       <c r="R17" t="n">
-        <v>6624359</v>
+        <v>6624275</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394292</v>
+        <v>121394279</v>
       </c>
       <c r="B18" t="n">
-        <v>95660</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2472,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559369</v>
+        <v>559456</v>
       </c>
       <c r="R18" t="n">
-        <v>6624275</v>
+        <v>6624254</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2538,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394279</v>
+        <v>121394299</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>95407</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,21 +2522,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2578,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559456</v>
+        <v>559316</v>
       </c>
       <c r="R19" t="n">
-        <v>6624254</v>
+        <v>6624382</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394299</v>
+        <v>121394281</v>
       </c>
       <c r="B20" t="n">
-        <v>95407</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,21 +2628,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2684,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559316</v>
+        <v>559438</v>
       </c>
       <c r="R20" t="n">
-        <v>6624382</v>
+        <v>6624241</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2750,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394281</v>
+        <v>121394282</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,112 +2817,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>121394282</v>
-      </c>
-      <c r="B22" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Vålboskogen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>559438</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6624241</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111171164</v>
+        <v>121394280</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålbo NNV, Vstm</t>
+          <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559374.474989331</v>
+        <v>559448</v>
       </c>
       <c r="R2" t="n">
-        <v>6624255.300735491</v>
+        <v>6624275</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En blommande+10-tal bladrosetter</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,61 +754,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gammal blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tom Sävström, Lennart Eriksson R, Mikael Mälberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121394258</v>
+        <v>121394283</v>
       </c>
       <c r="B3" t="n">
-        <v>94731</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559431</v>
+        <v>559438</v>
       </c>
       <c r="R3" t="n">
-        <v>6624255</v>
+        <v>6624241</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -912,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121394280</v>
+        <v>121394292</v>
       </c>
       <c r="B4" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +912,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559448</v>
+        <v>559369</v>
       </c>
       <c r="R4" t="n">
         <v>6624275</v>
@@ -1018,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121394254</v>
+        <v>121394296</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559346</v>
+        <v>559308</v>
       </c>
       <c r="R5" t="n">
-        <v>6624311</v>
+        <v>6624313</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,17 +1038,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1124,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121394291</v>
+        <v>121394298</v>
       </c>
       <c r="B6" t="n">
-        <v>90498</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559369</v>
+        <v>559319</v>
       </c>
       <c r="R6" t="n">
-        <v>6624275</v>
+        <v>6624359</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121394260</v>
+        <v>121394301</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559431</v>
+        <v>559363</v>
       </c>
       <c r="R7" t="n">
-        <v>6624255</v>
+        <v>6624449</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1336,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121394261</v>
+        <v>121394258</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559444</v>
+        <v>559431</v>
       </c>
       <c r="R8" t="n">
-        <v>6624248</v>
+        <v>6624255</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1442,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121394293</v>
+        <v>121394256</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>559369</v>
+        <v>559346</v>
       </c>
       <c r="R9" t="n">
-        <v>6624275</v>
+        <v>6624311</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1548,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121394263</v>
+        <v>121394265</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559444</v>
+        <v>559428</v>
       </c>
       <c r="R10" t="n">
-        <v>6624248</v>
+        <v>6624215</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,7 +1543,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1643,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1657,12 +1587,7 @@
         <v>121394278</v>
       </c>
       <c r="B11" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121394301</v>
+        <v>121394293</v>
       </c>
       <c r="B12" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559363</v>
+        <v>559369</v>
       </c>
       <c r="R12" t="n">
-        <v>6624449</v>
+        <v>6624275</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,54 +1786,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121394300</v>
+        <v>121394299</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vålboskogen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559350</v>
+        <v>559316</v>
       </c>
       <c r="R13" t="n">
-        <v>6624430</v>
+        <v>6624382</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121394283</v>
+        <v>121394291</v>
       </c>
       <c r="B14" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2016,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559438</v>
+        <v>559369</v>
       </c>
       <c r="R14" t="n">
-        <v>6624241</v>
+        <v>6624275</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2082,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121394256</v>
+        <v>121394254</v>
       </c>
       <c r="B15" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1101</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lotta Lundmark, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2188,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121394298</v>
+        <v>121394260</v>
       </c>
       <c r="B16" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>559319</v>
+        <v>559431</v>
       </c>
       <c r="R16" t="n">
-        <v>6624359</v>
+        <v>6624255</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2258,12 +2154,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2294,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121394292</v>
+        <v>121394279</v>
       </c>
       <c r="B17" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>559369</v>
+        <v>559456</v>
       </c>
       <c r="R17" t="n">
-        <v>6624275</v>
+        <v>6624254</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2400,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121394279</v>
+        <v>121394286</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>559456</v>
+        <v>559413</v>
       </c>
       <c r="R18" t="n">
-        <v>6624254</v>
+        <v>6624221</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2465,7 +2351,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2506,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121394299</v>
+        <v>121394290</v>
       </c>
       <c r="B19" t="n">
-        <v>95407</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>559316</v>
+        <v>559387</v>
       </c>
       <c r="R19" t="n">
-        <v>6624382</v>
+        <v>6624230</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2571,7 +2452,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2612,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121394281</v>
+        <v>121394297</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>559438</v>
+        <v>559308</v>
       </c>
       <c r="R20" t="n">
-        <v>6624241</v>
+        <v>6624313</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2677,7 +2553,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2696,6 +2572,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2718,37 +2595,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121394282</v>
+        <v>121394289</v>
       </c>
       <c r="B21" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>559438</v>
+        <v>559387</v>
       </c>
       <c r="R21" t="n">
-        <v>6624241</v>
+        <v>6624230</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2783,7 +2655,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Ramnäs</t>
+          <t>Sura</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2817,6 +2689,1295 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>98757373</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SO Bosjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>559357</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6624389</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hög höjd, kretsar österut.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121394261</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>559444</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6624248</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121394281</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>559438</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6624241</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121394284</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>559413</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6624221</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121394287</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>559387</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6624230</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121394263</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>559444</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6624248</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-02-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark, Lotta Lundmark</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121394282</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>559438</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6624241</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121394285</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>559413</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6624221</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121394288</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>559387</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6624230</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111171164</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vålbo NNV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>559374</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6624256</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En blommande+10-tal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal blandskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lennart Eriksson R, Mikael Mälberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>113361934</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vålbo NNV om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>559374</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6624255</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>U-Sur-0550</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-07-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>minst. 1 blommande + tiotal rosetter foto i AP OK</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>gammal blandskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lennart Eriksson R, Mikael Mälberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121394300</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vålboskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>559350</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6624430</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>

--- a/artfynd/A 20389-2024 artfynd.xlsx
+++ b/artfynd/A 20389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394280</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394283</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394292</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394301</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394256</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394265</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394278</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394293</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394299</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394291</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394254</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394260</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394279</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394290</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2592,6 +2687,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394297</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394289</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98757373</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2921,6 +3031,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394261</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3022,6 +3137,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394281</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3123,6 +3243,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394284</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3224,6 +3349,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394287</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3325,6 +3455,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394263</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394285</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3628,6 +3773,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394288</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3744,6 +3894,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111171164</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3877,6 +4032,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113361934</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3982,8 +4142,47 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>